--- a/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/3组磷硫铁法预实验-5-3.xlsx
+++ b/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/3组磷硫铁法预实验-5-3.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peiyuliu/Desktop/PKU-Undergraduate-Course-Public/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56EAD2E-65E1-974F-8124-0FD9BCD4AB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="120" windowWidth="9435" windowHeight="6915"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="板 1 - Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,7 +19,19 @@
     <definedName name="MethodPointer1">312770464</definedName>
     <definedName name="MethodPointer2">682</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -325,7 +343,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
       <sz val="10"/>
@@ -490,7 +508,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -552,17 +570,989 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$S$20:$S$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$U$20:$U$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>2.2080000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0365000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6745000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4485000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.145</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.62449999999999994</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.26350000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.10500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6196-C447-A4F3-C293A88BD026}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1979856416"/>
+        <c:axId val="1514132768"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1979856416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1514132768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1514132768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1979856416"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00FD6DC0-AB6D-C54F-828D-8A42AA49349C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -604,7 +1594,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -636,9 +1626,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -670,6 +1678,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -845,15 +1871,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:T42"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:U42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -861,7 +1887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="14">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -869,12 +1895,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="14">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="14">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -882,7 +1908,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="14">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,7 +1916,7 @@
         <v>45625</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="14">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -898,7 +1924,7 @@
         <v>0.75670138888888883</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="14">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,7 +1932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="14">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -914,7 +1940,7 @@
         <v>19012425</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="14">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -922,13 +1948,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" ht="14">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="14">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -936,12 +1962,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="14">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="14">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -949,7 +1975,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:21" ht="14">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
@@ -959,12 +1985,19 @@
       <c r="R17" s="9">
         <v>2.68</v>
       </c>
+      <c r="S17">
+        <v>0.2</v>
+      </c>
       <c r="T17">
-        <f>(P15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <f>(Q17+R17)/2</f>
+        <v>2.6375000000000002</v>
+      </c>
+      <c r="U17">
+        <f t="shared" ref="U17:U31" si="0">T17-0.057</f>
+        <v>2.5805000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="14">
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
@@ -974,8 +2007,19 @@
       <c r="R18" s="9">
         <v>2.4889999999999999</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="S18">
+        <v>0.18</v>
+      </c>
+      <c r="T18">
+        <f t="shared" ref="T18:T32" si="1">(Q18+R18)/2</f>
+        <v>2.4645000000000001</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="0"/>
+        <v>2.4075000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="14">
       <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
@@ -985,16 +2029,38 @@
       <c r="R19" s="13">
         <v>2.3220000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
+      <c r="S19">
+        <v>0.16</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="1"/>
+        <v>2.3980000000000001</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="0"/>
+        <v>2.3410000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="Q20" s="13">
         <v>2.3050000000000002</v>
       </c>
       <c r="R20" s="15">
         <v>2.2250000000000001</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
+      <c r="S20">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="1"/>
+        <v>2.2650000000000001</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="0"/>
+        <v>2.2080000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="14">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -1005,8 +2071,19 @@
       <c r="R21" s="17">
         <v>2.0590000000000002</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
+      <c r="S21">
+        <v>0.12</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="1"/>
+        <v>2.0935000000000001</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="0"/>
+        <v>2.0365000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="14">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
@@ -1019,16 +2096,38 @@
       <c r="R22" s="19">
         <v>1.714</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
+      <c r="S22">
+        <v>0.1</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="1"/>
+        <v>1.7315</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="0"/>
+        <v>1.6745000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="Q23" s="20">
         <v>1.466</v>
       </c>
       <c r="R23" s="19">
         <v>1.5449999999999999</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
+      <c r="S23">
+        <v>0.08</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="1"/>
+        <v>1.5055000000000001</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="0"/>
+        <v>1.4485000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="B24" s="6"/>
       <c r="C24" s="7">
         <v>1</v>
@@ -1072,8 +2171,19 @@
       <c r="R24" s="16">
         <v>1.18</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
+      <c r="S24">
+        <v>0.06</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="1"/>
+        <v>1.202</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="0"/>
+        <v>1.145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="14">
       <c r="B25" s="7" t="s">
         <v>25</v>
       </c>
@@ -1122,8 +2232,19 @@
       <c r="R25" s="8">
         <v>0.68300000000000005</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
+      <c r="S25">
+        <v>0.04</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="1"/>
+        <v>0.68149999999999999</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="0"/>
+        <v>0.62449999999999994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="14">
       <c r="B26" s="7" t="s">
         <v>26</v>
       </c>
@@ -1172,8 +2293,19 @@
       <c r="R26" s="12">
         <v>0.38500000000000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
+      <c r="S26">
+        <v>0.02</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="1"/>
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="0"/>
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="14">
       <c r="B27" s="7" t="s">
         <v>27</v>
       </c>
@@ -1222,8 +2354,19 @@
       <c r="R27" s="14">
         <v>0.378</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
+      <c r="S27">
+        <v>0.01</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="1"/>
+        <v>0.32050000000000001</v>
+      </c>
+      <c r="U27">
+        <f t="shared" si="0"/>
+        <v>0.26350000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="14">
       <c r="B28" s="7" t="s">
         <v>28</v>
       </c>
@@ -1272,8 +2415,19 @@
       <c r="R28" s="10">
         <v>0.16200000000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
+      <c r="S28" s="23">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="1"/>
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="U28">
+        <f t="shared" si="0"/>
+        <v>0.10500000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="14">
       <c r="B29" s="7" t="s">
         <v>29</v>
       </c>
@@ -1322,8 +2476,19 @@
       <c r="R29" s="10">
         <v>0.11700000000000001</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
+      <c r="S29" s="23">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="1"/>
+        <v>0.115</v>
+      </c>
+      <c r="U29">
+        <f t="shared" si="0"/>
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="14">
       <c r="B30" s="7" t="s">
         <v>30</v>
       </c>
@@ -1372,8 +2537,19 @@
       <c r="R30" s="10">
         <v>8.2000000000000003E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
+      <c r="S30" s="23">
+        <v>2E-3</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="1"/>
+        <v>8.1500000000000003E-2</v>
+      </c>
+      <c r="U30">
+        <f t="shared" si="0"/>
+        <v>2.4500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="14">
       <c r="B31" s="7" t="s">
         <v>31</v>
       </c>
@@ -1422,8 +2598,12 @@
       <c r="R31" s="8">
         <v>0.64300000000000002</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
+      <c r="U31">
+        <f t="shared" si="0"/>
+        <v>-5.7000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="14">
       <c r="B32" s="7" t="s">
         <v>32</v>
       </c>
@@ -1471,6 +2651,17 @@
       </c>
       <c r="R32" s="10">
         <v>0.05</v>
+      </c>
+      <c r="S32" s="23">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <f t="shared" si="1"/>
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="U32">
+        <f>T32-0.057</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -1512,7 +2703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" ht="14">
       <c r="A35" s="7" t="s">
         <v>25</v>
       </c>
@@ -1556,7 +2747,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" ht="14">
       <c r="A36" s="7" t="s">
         <v>26</v>
       </c>
@@ -1600,7 +2791,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" ht="14">
       <c r="A37" s="7" t="s">
         <v>27</v>
       </c>
@@ -1644,7 +2835,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" ht="14">
       <c r="A38" s="7" t="s">
         <v>28</v>
       </c>
@@ -1688,7 +2879,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" ht="14">
       <c r="A39" s="7" t="s">
         <v>29</v>
       </c>
@@ -1732,7 +2923,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" ht="14">
       <c r="A40" s="7" t="s">
         <v>30</v>
       </c>
@@ -1776,7 +2967,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" ht="14">
       <c r="A41" s="7" t="s">
         <v>31</v>
       </c>
@@ -1820,7 +3011,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" ht="14">
       <c r="A42" s="7" t="s">
         <v>32</v>
       </c>
@@ -1869,5 +3060,6 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="256" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>